--- a/IncuBrix_Submission_Form_Filled.xlsx
+++ b/IncuBrix_Submission_Form_Filled.xlsx
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>106 automated tests passing in ~1.7s</t>
+          <t>172 automated tests passing in ~2.0s</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
